--- a/data/trans_dic/IP18_E_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18_E_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,07; 91,43</t>
+          <t>80,39; 91,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,08; 94,11</t>
+          <t>83,23; 94,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,89; 93,47</t>
+          <t>82,29; 94,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39,5; 81,33</t>
+          <t>38,44; 82,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,98; 86,99</t>
+          <t>73,71; 87,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,82; 91,71</t>
+          <t>78,82; 91,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,99; 91,29</t>
+          <t>78,73; 90,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77,79; 100,0</t>
+          <t>77,46; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,62; 88,42</t>
+          <t>79,58; 88,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83,77; 91,87</t>
+          <t>83,49; 91,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82,73; 91,09</t>
+          <t>82,28; 90,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,82; 87,69</t>
+          <t>60,57; 88,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,19; 93,58</t>
+          <t>83,27; 94,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,82; 91,52</t>
+          <t>79,03; 91,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,24; 91,31</t>
+          <t>79,97; 91,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,11; 79,85</t>
+          <t>26,33; 79,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,65; 96,2</t>
+          <t>85,25; 95,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,03; 95,21</t>
+          <t>84,64; 95,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,57; 92,71</t>
+          <t>82,2; 92,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,06; 95,26</t>
+          <t>59,28; 94,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,21; 93,56</t>
+          <t>85,93; 93,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,62; 92,64</t>
+          <t>84,51; 92,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,3; 90,49</t>
+          <t>83,28; 91,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,82; 84,93</t>
+          <t>55,13; 83,66</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,93; 99,1</t>
+          <t>89,37; 99,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,57; 99,17</t>
+          <t>91,18; 98,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,65; 97,88</t>
+          <t>88,25; 97,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,58; 97,32</t>
+          <t>88,47; 97,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,29; 99,2</t>
+          <t>93,07; 99,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,2; 96,4</t>
+          <t>86,18; 96,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,93; 100,0</t>
+          <t>64,76; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,89; 97,43</t>
+          <t>91,33; 97,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94,34; 98,76</t>
+          <t>94,28; 98,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,2; 96,47</t>
+          <t>88,82; 96,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76,8; 100,0</t>
+          <t>76,44; 100,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,99; 96,81</t>
+          <t>90,92; 96,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,25; 97,9</t>
+          <t>92,81; 97,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,86; 97,47</t>
+          <t>92,7; 97,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,75; 100,0</t>
+          <t>86,2; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,52; 97,67</t>
+          <t>92,69; 97,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,81; 96,93</t>
+          <t>91,68; 96,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,98; 98,96</t>
+          <t>94,87; 98,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,18; 98,66</t>
+          <t>84,88; 98,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,01; 96,71</t>
+          <t>92,88; 96,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,21; 96,77</t>
+          <t>93,51; 96,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94,61; 97,82</t>
+          <t>94,62; 97,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,91; 97,93</t>
+          <t>88,26; 97,82</t>
         </is>
       </c>
     </row>
@@ -1277,37 +1277,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>95,73; 100,0</t>
+          <t>95,69; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,92; 100,0</t>
+          <t>95,72; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,79; 100,0</t>
+          <t>96,62; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83,24; 100,0</t>
+          <t>82,59; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,71; 100,0</t>
+          <t>94,97; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,26; 100,0</t>
+          <t>96,9; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,38; 99,57</t>
+          <t>95,41; 99,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>96,55; 99,58</t>
+          <t>96,52; 99,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97,43; 99,75</t>
+          <t>97,34; 99,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96,9; 99,53</t>
+          <t>97,08; 99,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,6; 100,0</t>
+          <t>93,21; 100,0</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,99; 98,26</t>
+          <t>89,14; 98,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,95; 98,73</t>
+          <t>89,5; 98,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,54; 98,95</t>
+          <t>89,95; 98,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,9; 100,0</t>
+          <t>68,27; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87,23; 97,82</t>
+          <t>87,55; 97,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,4; 100,0</t>
+          <t>94,82; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,7; 100,0</t>
+          <t>93,02; 100,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73,31; 100,0</t>
+          <t>66,5; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90,35; 97,39</t>
+          <t>90,49; 97,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94,62; 99,44</t>
+          <t>94,45; 99,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94,62; 99,41</t>
+          <t>94,1; 99,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79,84; 100,0</t>
+          <t>79,17; 100,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,3; 94,76</t>
+          <t>91,45; 94,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>93,02; 95,85</t>
+          <t>92,96; 95,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92,11; 95,22</t>
+          <t>92,28; 95,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73,57; 88,91</t>
+          <t>73,67; 89,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,25; 94,68</t>
+          <t>91,17; 94,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,28; 96,18</t>
+          <t>93,2; 96,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,51; 95,47</t>
+          <t>92,44; 95,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,1; 96,79</t>
+          <t>88,64; 96,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,96; 94,33</t>
+          <t>91,89; 94,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,59; 95,69</t>
+          <t>93,58; 95,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92,87; 95,02</t>
+          <t>92,93; 95,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,92; 92,69</t>
+          <t>84,19; 92,56</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75118; 85772</t>
+          <t>75420; 85828</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68619; 77731</t>
+          <t>68742; 77893</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62075; 71731</t>
+          <t>63154; 72195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9786; 20148</t>
+          <t>9522; 20329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>61625; 72460</t>
+          <t>61394; 72786</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69066; 79355</t>
+          <t>68205; 79301</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72271; 83523</t>
+          <t>72036; 82952</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15977; 20538</t>
+          <t>15908; 20538</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141016; 156603</t>
+          <t>140943; 156485</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141678; 155375</t>
+          <t>141193; 155162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139190; 153242</t>
+          <t>138431; 152280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27105; 39735</t>
+          <t>27444; 40068</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64917; 73916</t>
+          <t>65767; 74364</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70616; 80964</t>
+          <t>69917; 80979</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77780; 88510</t>
+          <t>77516; 88400</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2949; 8377</t>
+          <t>2762; 8336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62183; 69842</t>
+          <t>61890; 69370</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75218; 84221</t>
+          <t>74871; 84100</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80880; 90802</t>
+          <t>80508; 90821</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9565; 15428</t>
+          <t>9601; 15357</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130685; 141815</t>
+          <t>130254; 141508</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>149720; 163898</t>
+          <t>149518; 163640</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>162327; 176353</t>
+          <t>162289; 177372</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14363; 22666</t>
+          <t>14712; 22327</t>
         </is>
       </c>
     </row>
@@ -2343,17 +2343,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53393; 58835</t>
+          <t>53061; 58830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>75423; 81683</t>
+          <t>75099; 81454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48012; 53620</t>
+          <t>48343; 53645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2363,42 +2363,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75136; 82550</t>
+          <t>75045; 82532</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77164; 82941</t>
+          <t>77816; 82942</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57810; 64654</t>
+          <t>57801; 64561</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7641; 10926</t>
+          <t>7075; 10926</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>131062; 140491</t>
+          <t>131700; 140503</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>156580; 163920</t>
+          <t>156484; 163962</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108683; 117545</t>
+          <t>108223; 117208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11015; 14341</t>
+          <t>10962; 14341</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>152889; 162652</t>
+          <t>152770; 162324</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>178484; 187382</t>
+          <t>177646; 187492</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192473; 202041</t>
+          <t>192142; 201641</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25595; 30202</t>
+          <t>26034; 30202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>160973; 169931</t>
+          <t>161258; 169907</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>196894; 207864</t>
+          <t>196606; 207654</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>179535; 187051</t>
+          <t>179315; 187022</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35034; 40580</t>
+          <t>34912; 40508</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>318102; 330742</t>
+          <t>317658; 330692</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>378274; 392723</t>
+          <t>379519; 393541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>374917; 387642</t>
+          <t>374987; 387331</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63421; 69853</t>
+          <t>62958; 69779</t>
         </is>
       </c>
     </row>
@@ -2759,37 +2759,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82177; 85838</t>
+          <t>82135; 85838</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>132040; 137655</t>
+          <t>131764; 137655</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>120228; 124209</t>
+          <t>120006; 124209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17016; 20442</t>
+          <t>16882; 20442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>96078; 101443</t>
+          <t>96338; 101443</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>128810; 133814</t>
+          <t>129672; 133814</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>123046; 128450</t>
+          <t>123079; 128450</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,22 +2799,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180812; 186492</t>
+          <t>180761; 186593</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>264490; 270779</t>
+          <t>264257; 270554</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>245365; 252032</t>
+          <t>245817; 252127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47122; 50343</t>
+          <t>46922; 50343</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61348; 66984</t>
+          <t>60765; 66895</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47370; 51992</t>
+          <t>47130; 51992</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50983; 55714</t>
+          <t>50651; 55718</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6540; 9356</t>
+          <t>6388; 9356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57902; 64929</t>
+          <t>58115; 64838</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65494; 69378</t>
+          <t>65782; 69378</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57725; 61605</t>
+          <t>57307; 61605</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8556; 11671</t>
+          <t>7761; 11671</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>121570; 131034</t>
+          <t>121747; 130576</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>115477; 121354</t>
+          <t>115271; 120907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>111568; 117220</t>
+          <t>110957; 117151</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16788; 21028</t>
+          <t>16648; 21028</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>506003; 525139</t>
+          <t>506830; 525397</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>590812; 608761</t>
+          <t>590417; 609532</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>567654; 586810</t>
+          <t>568665; 587059</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>72594; 87739</t>
+          <t>72694; 88567</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>531562; 551516</t>
+          <t>531108; 550620</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>630764; 650389</t>
+          <t>630265; 649893</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>588474; 607319</t>
+          <t>588046; 607324</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>116158; 126177</t>
+          <t>115547; 125836</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1045354; 1072251</t>
+          <t>1044540; 1071758</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1227346; 1254932</t>
+          <t>1227208; 1254761</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1163134; 1189979</t>
+          <t>1163832; 1190497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>194508; 212288</t>
+          <t>192837; 212011</t>
         </is>
       </c>
     </row>
